--- a/data/trans_orig/P13_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P13_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2007</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13957</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33270</t>
+          <t>33607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>475527</t>
+          <t>475939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489475</t>
+          <t>489348</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>447476</t>
+          <t>447455</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>460895</t>
+          <t>460961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>928283</t>
+          <t>927946</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>947596</t>
+          <t>947444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24691</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36881</t>
+          <t>35590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>717983</t>
+          <t>719524</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>731429</t>
+          <t>731532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600803</t>
+          <t>601340</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>617196</t>
+          <t>616978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1324101</t>
+          <t>1325392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1345100</t>
+          <t>1345631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38614</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,82 +1434,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>22319</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13778</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33017</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>48223</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>35471</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>64384</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,67%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>22319</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14457</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>32707</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>48223</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>34847</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>62450</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600054</t>
+          <t>600159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621623</t>
+          <t>622246</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1547,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>667425</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>656727</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>675966</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,21%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1280189</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1264028</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1292941</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>96,37%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>95,15%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>97,33%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>667425</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>657037</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>675287</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1227</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1280189</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1265962</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1293565</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31199</t>
+          <t>32175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40926</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504201</t>
+          <t>504487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>515948</t>
+          <t>515670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484443</t>
+          <t>483467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502603</t>
+          <t>502620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>993863</t>
+          <t>994196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1015189</t>
+          <t>1015742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22032</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>23606</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47543</t>
+          <t>46947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364678</t>
+          <t>364697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379547</t>
+          <t>379441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>371972</t>
+          <t>371551</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390275</t>
+          <t>390617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>743153</t>
+          <t>743749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766183</t>
+          <t>767090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27423</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21104</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41340</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36066</t>
+          <t>35064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>60022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265160</t>
+          <t>262164</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281647</t>
+          <t>281444</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>301594</t>
+          <t>302088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>321830</t>
+          <t>322251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>573911</t>
+          <t>575495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>599451</t>
+          <t>600453</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31764</t>
+          <t>31020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>30781</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57536</t>
+          <t>56799</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49254</t>
+          <t>50210</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79851</t>
+          <t>82355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178119</t>
+          <t>178863</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>196010</t>
+          <t>196213</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>276372</t>
+          <t>277109</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302504</t>
+          <t>303127</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>463940</t>
+          <t>461436</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>494537</t>
+          <t>493581</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85961</t>
+          <t>86111</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125506</t>
+          <t>127563</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>137011</t>
+          <t>140887</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>189635</t>
+          <t>192328</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>238296</t>
+          <t>237495</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>303755</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3151037</t>
+          <t>3148980</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3190582</t>
+          <t>3190432</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3189562</t>
+          <t>3186869</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3242186</t>
+          <t>3238310</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6351986</t>
+          <t>6354738</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6417445</t>
+          <t>6418246</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2012</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>19957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32367</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435221</t>
+          <t>434189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448302</t>
+          <t>448258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>413217</t>
+          <t>413765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426345</t>
+          <t>426539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>852009</t>
+          <t>853920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>871481</t>
+          <t>871776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>25713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36215</t>
+          <t>35543</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30243</t>
+          <t>28013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54561</t>
+          <t>54689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>661340</t>
+          <t>661374</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>678170</t>
+          <t>677701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>573105</t>
+          <t>573777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>593747</t>
+          <t>593235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1241846</t>
+          <t>1241718</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1266164</t>
+          <t>1268394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39678</t>
+          <t>39664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>35397</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62352</t>
+          <t>62699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58970</t>
+          <t>59657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93862</t>
+          <t>95299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641238</t>
+          <t>641252</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661682</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647478</t>
+          <t>647131</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>675715</t>
+          <t>674433</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1296884</t>
+          <t>1295447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1331776</t>
+          <t>1331089</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>17128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38938</t>
+          <t>38972</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38626</t>
+          <t>40496</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67640</t>
+          <t>68573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61248</t>
+          <t>60487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97347</t>
+          <t>97861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>575679</t>
+          <t>575645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>597537</t>
+          <t>597489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>548559</t>
+          <t>547626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>577573</t>
+          <t>575703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1133469</t>
+          <t>1132955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1169568</t>
+          <t>1170329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27764</t>
+          <t>27383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>32523</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57656</t>
+          <t>59571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46285</t>
+          <t>46038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77209</t>
+          <t>77047</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>400635</t>
+          <t>401016</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>417783</t>
+          <t>418191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>390144</t>
+          <t>388229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>415858</t>
+          <t>415277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>798990</t>
+          <t>799152</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>829914</t>
+          <t>830161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38081</t>
+          <t>37825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43177</t>
+          <t>44677</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71215</t>
+          <t>72460</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66397</t>
+          <t>66519</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101848</t>
+          <t>100636</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271705</t>
+          <t>271961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292488</t>
+          <t>292572</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>282781</t>
+          <t>281536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>310819</t>
+          <t>309319</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>561934</t>
+          <t>563146</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>597385</t>
+          <t>597263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47544</t>
+          <t>46925</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81809</t>
+          <t>80929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118773</t>
+          <t>116505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112948</t>
+          <t>110066</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>154430</t>
+          <t>153707</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>201341</t>
+          <t>201960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>224821</t>
+          <t>224991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>269108</t>
+          <t>271376</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>306072</t>
+          <t>306952</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>482337</t>
+          <t>483060</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>523819</t>
+          <t>526701</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>135106</t>
+          <t>134333</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>188271</t>
+          <t>185836</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>296176</t>
+          <t>297009</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>369679</t>
+          <t>369396</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>444062</t>
+          <t>448149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>535778</t>
+          <t>534402</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3235565</t>
+          <t>3238000</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3288730</t>
+          <t>3289503</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3185578</t>
+          <t>3185861</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3259081</t>
+          <t>3258248</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6443315</t>
+          <t>6444691</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6535031</t>
+          <t>6530944</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2016</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2016 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14188</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414256</t>
+          <t>415688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383485</t>
+          <t>383205</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>393678</t>
+          <t>393176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>801030</t>
+          <t>802094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>812235</t>
+          <t>812156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>17993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>570722</t>
+          <t>572503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>584493</t>
+          <t>584773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>545184</t>
+          <t>545040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>557935</t>
+          <t>557857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1122977</t>
+          <t>1123372</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1140223</t>
+          <t>1140356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34440</t>
+          <t>37181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28479</t>
+          <t>28874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29380</t>
+          <t>29776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55217</t>
+          <t>56783</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633684</t>
+          <t>630943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654155</t>
+          <t>653544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>631175</t>
+          <t>630780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648576</t>
+          <t>647923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1272561</t>
+          <t>1270995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1298398</t>
+          <t>1298002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39565</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30877</t>
+          <t>29841</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56506</t>
+          <t>54997</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51998</t>
+          <t>53362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85543</t>
+          <t>86440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606483</t>
+          <t>607884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>628839</t>
+          <t>629130</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>591517</t>
+          <t>593026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>617146</t>
+          <t>618182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1208528</t>
+          <t>1207631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1242073</t>
+          <t>1240709</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26530</t>
+          <t>25307</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51741</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42131</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72331</t>
+          <t>72714</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>446416</t>
+          <t>447613</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465559</t>
+          <t>466447</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>445108</t>
+          <t>447629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>470319</t>
+          <t>471542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>902436</t>
+          <t>902053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>932636</t>
+          <t>933240</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15171</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34943</t>
+          <t>33164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24953</t>
+          <t>25942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49744</t>
+          <t>50798</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>312563</t>
+          <t>311182</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>327328</t>
+          <t>326754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342819</t>
+          <t>344598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>362591</t>
+          <t>362682</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>662348</t>
+          <t>661294</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>687139</t>
+          <t>686150</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33424</t>
+          <t>33989</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79710</t>
+          <t>77621</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67328</t>
+          <t>66143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103561</t>
+          <t>103990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>223574</t>
+          <t>223009</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241107</t>
+          <t>241357</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319188</t>
+          <t>321277</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>352445</t>
+          <t>353140</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>552335</t>
+          <t>551906</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>588568</t>
+          <t>589753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97926</t>
+          <t>96531</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>140090</t>
+          <t>140779</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>167866</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>223954</t>
+          <t>226190</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>280753</t>
+          <t>279351</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>353544</t>
+          <t>353703</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3253288</t>
+          <t>3252599</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3295452</t>
+          <t>3296847</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3315550</t>
+          <t>3313314</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3371638</t>
+          <t>3369504</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6579337</t>
+          <t>6579178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6652128</t>
+          <t>6653530</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2023</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390860</t>
+          <t>391131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307189</t>
+          <t>306700</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703588</t>
+          <t>703089</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713018</t>
+          <t>713020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>29750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>25562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46497</t>
+          <t>49055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393365</t>
+          <t>393797</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414837</t>
+          <t>414964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485924</t>
+          <t>485942</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504128</t>
+          <t>503983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>888554</t>
+          <t>885996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>914661</t>
+          <t>914733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30185</t>
+          <t>29401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47518</t>
+          <t>47039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506153</t>
+          <t>506937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524100</t>
+          <t>524783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>517994</t>
+          <t>518042</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>531198</t>
+          <t>531232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1030579</t>
+          <t>1031058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1053210</t>
+          <t>1052344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47465</t>
+          <t>45775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23729</t>
+          <t>24583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42218</t>
+          <t>43683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37346</t>
+          <t>34393</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81900</t>
+          <t>80731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>839317</t>
+          <t>841007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>876597</t>
+          <t>875748</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669479</t>
+          <t>668014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>687968</t>
+          <t>687114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1516579</t>
+          <t>1517748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1561133</t>
+          <t>1564086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26268</t>
+          <t>27229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48883</t>
+          <t>49120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,82 +11057,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>44573</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>36566</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>55513</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>10,14%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>81360</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>68440</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>96730</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>8,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>44573</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>35517</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53923</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>81360</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>66844</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>95955</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>511321</t>
+          <t>511084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>533936</t>
+          <t>532975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,82 +11170,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>502700</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>491760</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>510707</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>91,86%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>89,86%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1543</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1026117</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1010747</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1039037</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>92,65%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>91,27%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>502700</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>493350</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>511756</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,86%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>90,15%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>93,51%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1543</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1026117</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1011522</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1040633</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>91,34%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18972</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33847</t>
+          <t>34792</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55081</t>
+          <t>55124</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27875</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80513</t>
+          <t>81093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>332827</t>
+          <t>331882</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>347702</t>
+          <t>347899</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>553287</t>
+          <t>553244</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>593849</t>
+          <t>593942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>894529</t>
+          <t>893949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>947167</t>
+          <t>945146</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30220</t>
+          <t>30461</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49487</t>
+          <t>49128</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>94933</t>
+          <t>93195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120648</t>
+          <t>119333</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129996</t>
+          <t>129949</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161884</t>
+          <t>159794</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233272</t>
+          <t>233631</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>252539</t>
+          <t>252298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>303138</t>
+          <t>304453</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328853</t>
+          <t>330591</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>544661</t>
+          <t>546751</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>576549</t>
+          <t>576596</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>124843</t>
+          <t>130009</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196052</t>
+          <t>196862</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>202910</t>
+          <t>203776</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>280723</t>
+          <t>280250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>365723</t>
+          <t>361230</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>459618</t>
+          <t>459412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3260240</t>
+          <t>3259430</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3331449</t>
+          <t>3326283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3376864</t>
+          <t>3377337</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3454677</t>
+          <t>3453811</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6654261</t>
+          <t>6654467</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6748156</t>
+          <t>6752649</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P13_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>19062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>19662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>13193</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33607</t>
+          <t>31935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>475939</t>
+          <t>475002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489348</t>
+          <t>489460</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>447455</t>
+          <t>447827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>460961</t>
+          <t>460931</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>927946</t>
+          <t>929618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>947444</t>
+          <t>948360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>17826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>25267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15351</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35590</t>
+          <t>36994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>719524</t>
+          <t>717663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>730888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>601340</t>
+          <t>600227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>616978</t>
+          <t>616836</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1325392</t>
+          <t>1323988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1345631</t>
+          <t>1345331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16422</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38509</t>
+          <t>38467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,82 +1434,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>22319</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13700</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>34081</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>48223</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>34176</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>64056</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,57%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>22319</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13778</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>33017</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>48223</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>35471</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>64384</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600159</t>
+          <t>600201</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622246</t>
+          <t>621784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1547,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>667425</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>655663</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>676044</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,06%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,01%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1280189</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1264356</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1294236</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>96,37%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>97,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>667425</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>656727</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>675966</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1227</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1280189</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1264028</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1292941</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32175</t>
+          <t>31642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40593</t>
+          <t>40779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504487</t>
+          <t>503745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>515670</t>
+          <t>516195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>483467</t>
+          <t>484000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502620</t>
+          <t>502586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>994196</t>
+          <t>994010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1015742</t>
+          <t>1016299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22013</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>13771</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32435</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23606</t>
+          <t>24049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46947</t>
+          <t>47397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364697</t>
+          <t>365884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379441</t>
+          <t>379821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>371551</t>
+          <t>372261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390617</t>
+          <t>390215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>743749</t>
+          <t>743299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>767090</t>
+          <t>766647</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30419</t>
+          <t>27202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>19978</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35064</t>
+          <t>36920</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>62870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262164</t>
+          <t>265381</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281444</t>
+          <t>281236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>302088</t>
+          <t>303468</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>322251</t>
+          <t>322956</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>575495</t>
+          <t>572647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>600453</t>
+          <t>598597</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>12593</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31020</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30781</t>
+          <t>31974</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56799</t>
+          <t>57152</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>48681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82355</t>
+          <t>81259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178863</t>
+          <t>179296</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>196213</t>
+          <t>197290</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>277109</t>
+          <t>276756</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>303127</t>
+          <t>301934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>461436</t>
+          <t>462532</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>493581</t>
+          <t>495110</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86111</t>
+          <t>84933</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127563</t>
+          <t>127475</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140887</t>
+          <t>140324</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>192328</t>
+          <t>190043</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>237495</t>
+          <t>235509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>301003</t>
+          <t>302413</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3148980</t>
+          <t>3149068</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3190432</t>
+          <t>3191610</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3186869</t>
+          <t>3189154</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3238310</t>
+          <t>3238873</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6354738</t>
+          <t>6353328</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6418246</t>
+          <t>6420232</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>19104</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>12826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30456</t>
+          <t>30680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>434189</t>
+          <t>435042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448258</t>
+          <t>448603</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>413765</t>
+          <t>414171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426539</t>
+          <t>427144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>853920</t>
+          <t>853696</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>871776</t>
+          <t>871550</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25713</t>
+          <t>26700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35543</t>
+          <t>35907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54689</t>
+          <t>54832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>661374</t>
+          <t>660387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>677701</t>
+          <t>677825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>573777</t>
+          <t>573413</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>593235</t>
+          <t>593412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1241718</t>
+          <t>1241575</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1268394</t>
+          <t>1267490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18777</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39664</t>
+          <t>41153</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35397</t>
+          <t>33762</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62699</t>
+          <t>62429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59657</t>
+          <t>59634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95299</t>
+          <t>94225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641252</t>
+          <t>639763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>661835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647131</t>
+          <t>647401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>674433</t>
+          <t>676068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1295447</t>
+          <t>1296521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1331089</t>
+          <t>1331112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17128</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38972</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40496</t>
+          <t>38003</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>67213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60487</t>
+          <t>60926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97861</t>
+          <t>97898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>575645</t>
+          <t>576106</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>597489</t>
+          <t>597897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>547626</t>
+          <t>548986</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>575703</t>
+          <t>578196</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1132955</t>
+          <t>1132918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1170329</t>
+          <t>1169890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27383</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32523</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>59875</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46038</t>
+          <t>47009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77047</t>
+          <t>76901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401016</t>
+          <t>401466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418191</t>
+          <t>417761</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>388229</t>
+          <t>387925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>415277</t>
+          <t>415249</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>799152</t>
+          <t>799298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>830161</t>
+          <t>829190</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17214</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37825</t>
+          <t>36530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44677</t>
+          <t>44071</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72460</t>
+          <t>72862</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66519</t>
+          <t>67759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100636</t>
+          <t>102294</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271961</t>
+          <t>273256</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292572</t>
+          <t>293650</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>281536</t>
+          <t>281134</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>309319</t>
+          <t>309925</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>563146</t>
+          <t>561488</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>597263</t>
+          <t>596023</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23894</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46925</t>
+          <t>46635</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80929</t>
+          <t>80818</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116505</t>
+          <t>118797</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>110066</t>
+          <t>111320</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153707</t>
+          <t>155400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>201960</t>
+          <t>202250</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>224991</t>
+          <t>225444</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>271376</t>
+          <t>269084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>306952</t>
+          <t>307063</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>483060</t>
+          <t>481367</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>526701</t>
+          <t>525447</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134333</t>
+          <t>135453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>185836</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>297009</t>
+          <t>299047</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>369396</t>
+          <t>365052</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>448149</t>
+          <t>443214</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>534402</t>
+          <t>537191</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3238000</t>
+          <t>3233077</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3289503</t>
+          <t>3288383</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3185861</t>
+          <t>3190205</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3258248</t>
+          <t>3256210</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6444691</t>
+          <t>6441902</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6530944</t>
+          <t>6535879</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415688</t>
+          <t>414204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383205</t>
+          <t>383402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>393176</t>
+          <t>393668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>802094</t>
+          <t>800934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>812156</t>
+          <t>812225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>572503</t>
+          <t>572128</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>584773</t>
+          <t>584803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>545040</t>
+          <t>546771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>557857</t>
+          <t>558071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1123372</t>
+          <t>1123800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1140356</t>
+          <t>1140921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>34560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,82 +7392,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>18412</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11546</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>29154</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>41347</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>29001</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>56955</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,18%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>18412</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11731</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>28874</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>41347</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>29776</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>56783</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630943</t>
+          <t>633564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653544</t>
+          <t>653262</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,82 +7505,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>641242</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>630500</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>648108</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1286431</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1270823</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1298777</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>96,89%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>97,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>641242</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>630780</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>647923</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1263</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1286431</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1270995</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1298002</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>37863</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29841</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54997</t>
+          <t>56441</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53362</t>
+          <t>51321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86440</t>
+          <t>86189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607884</t>
+          <t>608185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>629130</t>
+          <t>628795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593026</t>
+          <t>591582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>618182</t>
+          <t>618078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1207631</t>
+          <t>1207882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1240709</t>
+          <t>1242750</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>31196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25307</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49220</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>42060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72714</t>
+          <t>72553</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>447613</t>
+          <t>446722</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466447</t>
+          <t>465993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>447629</t>
+          <t>446820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>471542</t>
+          <t>470162</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>902053</t>
+          <t>902214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>933240</t>
+          <t>932707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>23034</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33164</t>
+          <t>33643</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>26198</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50798</t>
+          <t>51089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311182</t>
+          <t>311296</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>326754</t>
+          <t>326606</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>344598</t>
+          <t>344119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>362682</t>
+          <t>363391</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>661294</t>
+          <t>661003</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>686150</t>
+          <t>685894</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15641</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33989</t>
+          <t>32929</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45758</t>
+          <t>44719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77621</t>
+          <t>77974</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66143</t>
+          <t>66640</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103990</t>
+          <t>102968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>223009</t>
+          <t>224069</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241357</t>
+          <t>241644</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>321277</t>
+          <t>320924</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>353140</t>
+          <t>354179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>551906</t>
+          <t>552928</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>589753</t>
+          <t>589256</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96531</t>
+          <t>96776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>140779</t>
+          <t>141560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>168680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>226190</t>
+          <t>224144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>279351</t>
+          <t>281018</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>353703</t>
+          <t>352040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3252599</t>
+          <t>3251818</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3296847</t>
+          <t>3296602</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3313314</t>
+          <t>3315360</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3369504</t>
+          <t>3370824</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6579178</t>
+          <t>6580841</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6653530</t>
+          <t>6651863</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>398225</t>
+          <t>402951</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391131</t>
+          <t>390700</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,17 +9813,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>312047</t>
+          <t>361188</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>306700</t>
+          <t>354405</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>710272</t>
+          <t>764139</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703089</t>
+          <t>751329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713020</t>
+          <t>768991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>12152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>35673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>16389</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25562</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>31890</t>
+          <t>37543</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>25012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49055</t>
+          <t>53789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>406451</t>
+          <t>455736</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393797</t>
+          <t>441217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414964</t>
+          <t>464738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>496709</t>
+          <t>484694</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485942</t>
+          <t>473744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503983</t>
+          <t>491512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>903161</t>
+          <t>940430</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>885996</t>
+          <t>924184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>914733</t>
+          <t>952961</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,102 +10351,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>11494</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29401</t>
+          <t>29282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17928</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11892</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25930</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>37438</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>26715</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>49074</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15858</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10526</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23716</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>34844</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>25753</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>47039</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -10464,102 +10464,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>517352</t>
+          <t>601327</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506937</t>
+          <t>591555</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524783</t>
+          <t>609343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>603430</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>595428</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>609466</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,83%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1204757</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1193121</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1215480</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>820</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>525900</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>518042</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>531232</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1043253</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1031058</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1052344</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541758</t>
+          <t>621358</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541758</t>
+          <t>621358</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541758</t>
+          <t>621358</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078097</t>
+          <t>1242195</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078097</t>
+          <t>1242195</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078097</t>
+          <t>1242195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28435</t>
+          <t>30243</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45775</t>
+          <t>43027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33101</t>
+          <t>36576</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24583</t>
+          <t>27599</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>46823</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>66819</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34393</t>
+          <t>52610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80731</t>
+          <t>86034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>858347</t>
+          <t>669440</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>841007</t>
+          <t>656656</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>875748</t>
+          <t>679580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>678596</t>
+          <t>699070</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>668014</t>
+          <t>688823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>687114</t>
+          <t>708047</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1536943</t>
+          <t>1368511</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1517748</t>
+          <t>1349296</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1564086</t>
+          <t>1382720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886782</t>
+          <t>699683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711697</t>
+          <t>735646</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711697</t>
+          <t>735646</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711697</t>
+          <t>735646</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598479</t>
+          <t>1435330</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598479</t>
+          <t>1435330</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598479</t>
+          <t>1435330</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36787</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27229</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49120</t>
+          <t>52471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44573</t>
+          <t>50711</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>40590</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55513</t>
+          <t>61840</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,17 +11107,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>81360</t>
+          <t>89408</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68440</t>
+          <t>74393</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96730</t>
+          <t>106433</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>523417</t>
+          <t>569568</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>511084</t>
+          <t>555794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>532975</t>
+          <t>579348</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>502700</t>
+          <t>557459</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>491760</t>
+          <t>546330</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>510707</t>
+          <t>567580</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,17 +11220,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1026117</t>
+          <t>1127026</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1010747</t>
+          <t>1110001</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1039037</t>
+          <t>1142041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547273</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547273</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547273</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1107477</t>
+          <t>1216434</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107477</t>
+          <t>1216434</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1107477</t>
+          <t>1216434</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25776</t>
+          <t>28269</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18775</t>
+          <t>20235</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34792</t>
+          <t>37021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33971</t>
+          <t>39160</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55124</t>
+          <t>48341</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>59747</t>
+          <t>67429</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>55564</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81093</t>
+          <t>80318</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>340898</t>
+          <t>377154</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>331882</t>
+          <t>368402</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>347899</t>
+          <t>385188</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>574397</t>
+          <t>400006</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>553244</t>
+          <t>390825</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>593942</t>
+          <t>407888</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>915295</t>
+          <t>777160</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>893949</t>
+          <t>764271</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>945146</t>
+          <t>789025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366674</t>
+          <t>405423</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366674</t>
+          <t>405423</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366674</t>
+          <t>405423</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975042</t>
+          <t>844589</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975042</t>
+          <t>844589</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975042</t>
+          <t>844589</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>39239</t>
+          <t>41736</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30461</t>
+          <t>33463</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49128</t>
+          <t>53105</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>106627</t>
+          <t>116063</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93195</t>
+          <t>101884</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>119333</t>
+          <t>129696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>145865</t>
+          <t>157798</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129949</t>
+          <t>141272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159794</t>
+          <t>174569</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>243520</t>
+          <t>268462</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233631</t>
+          <t>257093</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>252298</t>
+          <t>276735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>317159</t>
+          <t>346350</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>304453</t>
+          <t>332717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330591</t>
+          <t>360529</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>560680</t>
+          <t>614813</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>546751</t>
+          <t>598042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>576596</t>
+          <t>631339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423786</t>
+          <t>462413</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423786</t>
+          <t>462413</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423786</t>
+          <t>462413</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706545</t>
+          <t>772611</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706545</t>
+          <t>772611</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706545</t>
+          <t>772611</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>168081</t>
+          <t>184452</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130009</t>
+          <t>160618</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196862</t>
+          <t>213718</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>250076</t>
+          <t>278150</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>203776</t>
+          <t>253214</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>280250</t>
+          <t>305625</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>418157</t>
+          <t>462601</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>361230</t>
+          <t>427953</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>459412</t>
+          <t>501471</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3288211</t>
+          <t>3344637</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3259430</t>
+          <t>3315371</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3326283</t>
+          <t>3368471</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3407511</t>
+          <t>3452198</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3377337</t>
+          <t>3424723</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3453811</t>
+          <t>3477134</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6695722</t>
+          <t>6796837</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6654467</t>
+          <t>6757967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6752649</t>
+          <t>6831485</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456292</t>
+          <t>3529089</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657587</t>
+          <t>3730348</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7113879</t>
+          <t>7259438</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
